--- a/docs/Lizmo_Backlog.xlsx
+++ b/docs/Lizmo_Backlog.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$I$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -159,6 +159,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -554,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4215,8 +4218,863 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>LZ-150</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to record the deposit and advance at lease start so that the standard arrangement is captured</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Deposit and advance amounts held against the lease, separate from rent; both visible to the tenant</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>LZ-151</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want advance rent applied automatically so that the first months are not billed twice</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Advance offsets the earliest periods; remaining advance visible until consumed</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LZ-152</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>As a tenant, I want to see what deposit is held so that I know what should come back</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Deposit balance shown on the lease, with any deductions itemised</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LZ-153</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to deduct unpaid rent or damage from the deposit so that settlement is accurate</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Itemised deductions with reason and amount; cannot exceed the deposit held</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>LZ-154</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>As a tenant, I want the balance of my deposit refunded on record so that there is no dispute later</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Refund recorded with date, amount and method; lease shows a zero balance afterwards</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>LZ-160</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to define which utilities I charge for so that billing matches my property</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Utility types configured per property with a unit rate; unused types stay hidden</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>LZ-161</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to record meter readings so that charges reflect actual consumption</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Previous and current reading captured per unit; consumption derived, never entered</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>LZ-162</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want shared utilities split across occupied beds so that bedspacers pay their share</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Shared charge divided across beds occupied during the period; vacant beds excluded</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>LZ-163</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want utilities added to the billing period so that the tenant settles one amount</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Period total covers rent plus utilities; the breakdown remains visible</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>LZ-164</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>As a tenant, I want to see how my utility charge was calculated so that I can trust it</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Readings, rate and consumption shown; shared charges show the split basis</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>LZ-170</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to invite a tenant to their lease so that they can access it themselves</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Invite issued to email or phone; single-use and time-limited</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>LZ-171</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>As an invited tenant, I want to claim my lease when I sign up so that my records appear immediately</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Claiming attaches the lease to the new account; invite cannot be reused</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>LZ-172</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to create an account for a tenant who cannot so that no one is excluded</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Landlord-created account with a temporary credential the tenant must change on first sign-in</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>LZ-173</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>As a returning tenant, I want a new lease attached to my existing account so that I keep my history</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Invite to a known email or phone links to the existing profile rather than duplicating it</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>LZ-174</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to revoke an unclaimed invite so that a wrong number cannot claim a lease</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Revoked and expired invites are refused at claim time</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>LZ-180</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Move-out &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want to start a move-out so that the final balance is worked out before the tenant leaves</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Move-out date set; further periods stop generating for that lease</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>LZ-181</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Move-out &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>As a tenant, I want a final statement so that I know exactly what I owe or am owed</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Unpaid periods, utility charges and deductions netted against the deposit held</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>LZ-182</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Move-out &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want the bed released on settlement so that I can re-let it</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Bed returns to VACANT; the slot leaves the next platform billing snapshot</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>LZ-183</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Move-out &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>As a landlord, I want move-out history retained so that past tenancies remain auditable</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Ended leases, their periods and payments stay queryable after the bed is re-let</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4227,7 +5085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4283,586 +5141,734 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Foundation &amp; Developer Experience</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>The stack runs locally, the schema is versioned, and contracts are generated rather than hand-kept</t>
         </is>
       </c>
-      <c r="D2" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B2)</f>
-        <v/>
-      </c>
-      <c r="E2" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B2,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F2" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B2,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G2" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B2,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B2,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F2" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B2,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G2" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B2,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H2" s="13">
         <f>IF($E2=0,0,$G2/$E2)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Design System</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>One visual language, shared by both clients, matching design language v2</t>
         </is>
       </c>
-      <c r="D3" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B3)</f>
-        <v/>
-      </c>
-      <c r="E3" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B3,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F3" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B3,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G3" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B3,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H3" s="12">
+      <c r="D3" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B3)</f>
+        <v/>
+      </c>
+      <c r="E3" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B3,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F3" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B3,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G3" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B3,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H3" s="13">
         <f>IF($E3=0,0,$G3/$E3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Accounts &amp; Access</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Identity, sessions, and the authorisation rules that keep landlords and tenants apart</t>
         </is>
       </c>
-      <c r="D4" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B4,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F4" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B4,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G4" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B4,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H4" s="12">
+      <c r="D4" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B4,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F4" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B4,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G4" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B4,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H4" s="13">
         <f>IF($E4=0,0,$G4/$E4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Property, Unit &amp; Bed</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>The rentable inventory, including bedspaces as first-class things</t>
         </is>
       </c>
-      <c r="D5" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B5,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B5,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B5,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H5" s="12">
+      <c r="D5" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B5,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B5,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B5,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H5" s="13">
         <f>IF($E5=0,0,$G5/$E5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Leases</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Attaching a tenant to a unit or bed, with landlord-controlled due dates</t>
         </is>
       </c>
-      <c r="D6" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B6,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B6,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B6,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H6" s="12">
+      <c r="D6" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B6,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B6,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B6,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H6" s="13">
         <f>IF($E6=0,0,$G6/$E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Billing &amp; Payments</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Rent tracked per period and settled by proof-of-payment, with no gateway</t>
         </is>
       </c>
-      <c r="D7" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B7,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B7,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B7,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H7" s="12">
+      <c r="D7" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B7,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B7,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B7,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H7" s="13">
         <f>IF($E7=0,0,$G7/$E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Tenants report problems in plain words; landlords track them to done</t>
         </is>
       </c>
-      <c r="D8" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B8,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B8,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B8,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
+      <c r="D8" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B8,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B8,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B8,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H8" s="13">
         <f>IF($E8=0,0,$G8/$E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>E8</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Per-property caretakers with granular, revocable permissions</t>
         </is>
       </c>
-      <c r="D9" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B9,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B9,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B9,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H9" s="12">
+      <c r="D9" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B9,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B9,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B9,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H9" s="13">
         <f>IF($E9=0,0,$G9/$E9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>E9</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Contracts, IDs and receipts attached to the record they belong to</t>
         </is>
       </c>
-      <c r="D10" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B10,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B10,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B10,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
+      <c r="D10" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B10,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B10,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B10,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H10" s="13">
         <f>IF($E10=0,0,$G10/$E10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Notices</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Announcements with dynamic audience, expiry and read receipts</t>
         </is>
       </c>
-      <c r="D11" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B11,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B11,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B11,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H11" s="12">
+      <c r="D11" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B11,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B11,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B11,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H11" s="13">
         <f>IF($E11=0,0,$G11/$E11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>In-app signals for rent, payments, maintenance and notices</t>
         </is>
       </c>
-      <c r="D12" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B12,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B12,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B12,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H12" s="12">
+      <c r="D12" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B12,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B12,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B12,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H12" s="13">
         <f>IF($E12=0,0,$G12/$E12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Occupancy, income, overdue and maintenance views over live data</t>
         </is>
       </c>
-      <c r="D13" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B13,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F13" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B13,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B13,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H13" s="12">
+      <c r="D13" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B13,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B13,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B13,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H13" s="13">
         <f>IF($E13=0,0,$G13/$E13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Platform Billing</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Lizmo's own revenue: per-slot invoicing, collection and enforcement</t>
         </is>
       </c>
-      <c r="D14" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B14,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B14,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B14,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H14" s="12">
+      <c r="D14" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B14,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B14,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B14,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H14" s="13">
         <f>IF($E14=0,0,$G14/$E14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Admin Console</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Internal tooling for verifying platform payments and chasing overdue accounts</t>
         </is>
       </c>
-      <c r="D15" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B15,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B15,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B15,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H15" s="12">
+      <c r="D15" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B15,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B15,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B15,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H15" s="13">
         <f>IF($E15=0,0,$G15/$E15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>E15</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Deployment &amp; Operations</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Reproducible infrastructure, automated releases and basic observability</t>
         </is>
       </c>
-      <c r="D16" s="11">
-        <f>COUNTIF(Backlog!$B$2:$B$81,$B16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>SUMIF(Backlog!$B$2:$B$81,$B16,Backlog!$G$2:$G$81)</f>
-        <v/>
-      </c>
-      <c r="F16" s="11">
-        <f>COUNTIFS(Backlog!$B$2:$B$81,$B16,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>SUMIFS(Backlog!$G$2:$G$81,Backlog!$B$2:$B$81,$B16,Backlog!$H$2:$H$81,"Done")</f>
-        <v/>
-      </c>
-      <c r="H16" s="12">
+      <c r="D16" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B16,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B16,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B16,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H16" s="13">
         <f>IF($E16=0,0,$G16/$E16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Deposits &amp; Advance Rent</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>The standard PH arrangement of deposit plus advance, held, drawn down and refunded</t>
+        </is>
+      </c>
+      <c r="D17" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B17,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B17,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B17,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H17" s="13">
+        <f>IF($E17=0,0,$G17/$E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Utilities &amp; Shared Costs</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Sub-metered electricity and water billed alongside rent, split fairly across bedspaces</t>
+        </is>
+      </c>
+      <c r="D18" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B18,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B18,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B18,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H18" s="13">
+        <f>IF($E18=0,0,$G18/$E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Tenant Onboarding</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>How a tenant actually gets an account and reaches their own lease</t>
+        </is>
+      </c>
+      <c r="D19" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B19,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F19" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B19,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B19,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H19" s="13">
+        <f>IF($E19=0,0,$G19/$E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Move-out &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Ending a tenancy with the money resolved, not just the bed freed</t>
+        </is>
+      </c>
+      <c r="D20" s="12">
+        <f>COUNTIF(Backlog!$B$2:$B$100,$B20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>SUMIF(Backlog!$B$2:$B$100,$B20,Backlog!$G$2:$G$100)</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>COUNTIFS(Backlog!$B$2:$B$100,$B20,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>SUMIFS(Backlog!$G$2:$G$100,Backlog!$B$2:$B$100,$B20,Backlog!$H$2:$H$100,"Done")</f>
+        <v/>
+      </c>
+      <c r="H20" s="13">
+        <f>IF($E20=0,0,$G20/$E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="15">
-        <f>SUM(D2:D17)</f>
-        <v/>
-      </c>
-      <c r="E17" s="15">
-        <f>SUM(E2:E17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="15">
-        <f>SUM(F2:F17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="15">
-        <f>SUM(G2:G17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="16">
-        <f>IF($E17=0,0,$G17/$E17)</f>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="16">
+        <f>SUM(D2:D21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>SUM(E2:E21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>SUM(F2:F21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>SUM(G2:G21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>IF($E21=0,0,$G21/$E21)</f>
         <v/>
       </c>
     </row>
@@ -4877,7 +5883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5174,13 +6180,30 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Spec ref</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Not covered by either spec. Needs a product decision before it can be built, and the schema has no representation for it yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Statuses reflect the repository as of 14 Aug 2026. Stories are derived from Lizmo_Product_Spec_v1.md and Lizmo_Tech_Spec_v1.md; estimates are first-pass and unvalidated by any completed sprint.</t>
         </is>
@@ -5188,7 +6211,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
